--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI/ Edge Computing SW Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1b35fbc6e0f065e</t>
+          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Certified NVIDIA AI Infrastructure &amp; Kubernetes Platform Engineer</t>
+          <t>Data Scientist Intern/Data Science Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IT Search Corp</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, PyTorch, XGBoost, S3, EC2, Data Lake, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e262aed548e90d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Applied Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Git, Snowflake, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,77 +566,287 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13ca5a9085e4ba28</t>
+          <t>https://www.indeed.com/viewjob?jk=7254b8c266ea6043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Feature Engineering</t>
+          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Git, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62068a6428147556</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IT DevSecOps Engineer</t>
+          <t>AI Agents Applied Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=751098e90061ea5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr Infrastructure Developer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applied AIML Data Scientist-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a792d18781a0ae9e</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44790e38d1f2e1a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hummingbird</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Terraform, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f173e454576b855</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0e34c832675c165</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Third Sector Intelligence</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TensorFlow, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Investment Risk &amp; Analytics - Quant Modeling Senior Associate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Tableau, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=196fdc85c8eb8654</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,54 +496,54 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129a771826f3124f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist Intern/Data Science Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, XGBoost, S3, EC2, Data Lake, Docker, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, FastAPI, Docker, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f21f9ffc85f99a93</t>
+          <t>https://www.indeed.com/viewjob?jk=a6264837b9ad3a1f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Applied Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Autnhive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7254b8c266ea6043</t>
+          <t>https://www.indeed.com/viewjob?jk=77dff285c9d5a43e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (JavaScript, AWS, Snowflake)</t>
+          <t>Sr Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>ThoughtFocus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
+          <t>S3, EC2, Data Lake, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa1bd38d503b5f5</t>
+          <t>https://www.indeed.com/viewjob?jk=071b0987d8e950fc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Agents Applied Engineer - Senior Associate</t>
+          <t>Senior Associate, Data Scientist - US Card (Applied GenAI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751098e90061ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7742fcf405e12beb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Infrastructure Developer</t>
+          <t>Senior Machine Learning Engineer - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c10e25f49712691</t>
+          <t>https://www.indeed.com/viewjob?jk=451c5757e688b4bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AIML Data Scientist-Senior Associate</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Disney Direct to Consumer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44790e38d1f2e1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2624e59e2876f03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>AI Engineering Internship</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hummingbird</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Terraform, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f173e454576b855</t>
+          <t>https://www.indeed.com/viewjob?jk=2a84894550b7fb6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III (Full Stack) – API Gateway Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Docker, Kubernetes, Git, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e34c832675c165</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Third Sector Intelligence</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TensorFlow, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11052963eea20287</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Investment Risk &amp; Analytics - Quant Modeling Senior Associate</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Tableau, Power BI, Python, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=196fdc85c8eb8654</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7fc2553f71b2fa</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Warrenton, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0ceb630e33d4ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1d393e51b035c281</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FastAPI, Docker, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6264837b9ad3a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ffb1cf3c611caa16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Autnhive</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77dff285c9d5a43e</t>
+          <t>https://www.indeed.com/viewjob?jk=d159eb3c059fcbe4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Ops Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ThoughtFocus</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, EC2, Data Lake, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, PostgreSQL, MySQL, MongoDB, Tableau, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b0987d8e950fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b953f40d995bb17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - US Card (Applied GenAI)</t>
+          <t>Senior Research Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7742fcf405e12beb</t>
+          <t>https://www.indeed.com/viewjob?jk=b32ece3c1be3af7c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Data Science Senior Associate - Card Data Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451c5757e688b4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aafeecd03f16fbb9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Data Analyst, Growth &amp; Acquisition</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Direct to Consumer</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala, Optimization</t>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2624e59e2876f03</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Engineering Internship</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Synopsys</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a84894550b7fb6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7fc2553f71b2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9e1f42f5d16e01</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warrenton, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d393e51b035c281</t>
+          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineer (Linux, Hardware, Security, DevOps/Automation) - TS/SCI w/ Poly</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Versigent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffb1cf3c611caa16</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d4f2ad50e62692</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Software Engineer Data Warehouse</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>New Meridian Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, S3, Redshift, BigQuery, Docker, Git, Snowflake, BigQuery, Redshift, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d159eb3c059fcbe4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr. Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Kutir Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, PostgreSQL, MySQL, MongoDB, Tableau, Quicksight, Python, SQL</t>
+          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b953f40d995bb17</t>
+          <t>https://www.indeed.com/viewjob?jk=082e9578333bb1fb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Research Software Engineer</t>
+          <t>Sr. Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Kutir Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32ece3c1be3af7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a2954cbf5577991</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Card Data Analytics</t>
+          <t>Senior Software Engineer AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,357 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafeecd03f16fbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2c7f2e3075f4ea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Growth &amp; Acquisition</t>
+          <t>Azure Data Engineer with AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Athena</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wilmington, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Athena, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b2707a7d2a34a36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Zendesk</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Git, Snowflake, BigQuery, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Clarip</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Docker, Hadoop, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69f5657981d550d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Entry-Level Software Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Customer Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dc480483af599e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Specialist - Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9e1f42f5d16e01</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c425441b2f640d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Quality Engineering</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98ce50c47a0d66f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer (C/C++) - Viasat Government</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Duluth, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, C++</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53893e0438045f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Analyst (Central Analytics)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CI/CD, Snowflake, Python, SQL, R, Scala, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Pinecone, TensorFlow, PyTorch, XGBoost, Kinesis, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda8d7d5a74ae53f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI or ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Versigent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d4f2ad50e62692</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Data Warehouse</t>
+          <t>Sr. Machine Learning Engineer (copy)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New Meridian Corporation</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Docker, Git, Snowflake, BigQuery, Redshift, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3ea4ad70ff630c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with AI</t>
+          <t>#22161 - Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kutir Corporation</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082e9578333bb1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c538f30b00a42a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with AI</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kutir Corporation</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, MLflow, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2954cbf5577991</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2914df08fd1429</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Java</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2c7f2e3075f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a1828374aa7504d0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with AI</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, Data Lake, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603571b168320d09</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf7f2fc21997a1c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Athena, Snowflake, Python, SQL, R</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2707a7d2a34a36</t>
+          <t>https://www.indeed.com/viewjob?jk=3691403890861ce1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Ryder System</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, Snowflake, BigQuery, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, AWS SageMaker, Data Lake, Git, Databricks, Tableau, Power BI, MicroStrategy, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423f52012afc9797</t>
+          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clarip</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Hadoop, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f5657981d550d0</t>
+          <t>https://www.indeed.com/viewjob?jk=18e8fe2344ea1b85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entry-Level Software Engineer (HYBRID)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Children's Hospital of Philadelphia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, CI/CD, Git, Kafka, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eb29038f237e311</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Customer Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, FastAPI, Docker, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, MLflow, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dc480483af599e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c681d355fb14c2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist - Quality Engineering</t>
+          <t>Software Dev Engineer II - 1Finity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c425441b2f640d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5db40012ec588099</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98ce50c47a0d66f6</t>
+          <t>https://www.indeed.com/viewjob?jk=84af8a7a7b4d9137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer (C/C++) - Viasat Government</t>
+          <t>Senior Data Scientist - GenAI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Cover Genius</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, C++</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53893e0438045f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1ace319434b29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst (Central Analytics)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cadre5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CI/CD, Snowflake, Python, SQL, R, Scala, Optimization, Bayesian, Hypothesis Testing</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,182 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b00017f96539a3</t>
+          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend - Platform (Overseer)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, AKS, Kafka, MongoDB, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7347970c571437b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II - SDLC, GenAI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, AKS, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fb2f369f691c242</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Software Development Eng</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, MLflow, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b853965575396d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr Software Development Eng</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Databricks, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e5d119a8e84a74e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Analyst, Applied AI Solutions</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aecd19983b185544</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Palantir AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bain Capital</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Pinecone, TensorFlow, PyTorch, XGBoost, Kinesis, MLflow</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Glue, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d62fc510f17558</t>
+          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI or ML Engineer - Remote</t>
+          <t>Data Analytics Engineer (AI/ML Focus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
+          <t>Data Scientist, Pinecone, TensorFlow, PyTorch, S3, Glue, Redshift, Databricks, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe560b8dc00ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (copy)</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, Terraform, Git, Snowflake</t>
+          <t>Data Scientist, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c26d512d400fb40</t>
+          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#22161 - Senior AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c538f30b00a42a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6c926cca4a747050</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Software Engineer - AI Platform Team</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Glue, CI/CD, Git, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2914df08fd1429</t>
+          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Oak Ridge National Laboratory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1828374aa7504d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c68121d4859f1b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Kin Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf7f2fc21997a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=651d0a0b21d7c611</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691403890861ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=f745acfa6c4033a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Software Engineer - .NET Full Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, AWS SageMaker, Data Lake, Git, Databricks, Tableau, Power BI, MicroStrategy, Python</t>
+          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e10b65eb3e9642b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e8fe2344ea1b85</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d608da55724e2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Children's Hospital of Philadelphia</t>
+          <t>Electrosoft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, CI/CD, Git, Kafka, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffce82525f57f21</t>
+          <t>https://www.indeed.com/viewjob?jk=424ec8adc24cf26f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bain Capital</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, XGBoost, MLflow, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c681d355fb14c2</t>
+          <t>https://www.indeed.com/viewjob?jk=25d100d0ad919c12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Dev Engineer II - 1Finity</t>
+          <t>Software Engineer, Real-Time Communications (CCaaS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Port Richey, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db40012ec588099</t>
+          <t>https://www.indeed.com/viewjob?jk=638e82497dbabdbe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Innovation Software Engineer L3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84af8a7a7b4d9137</t>
+          <t>https://www.indeed.com/viewjob?jk=84788d0b728d3cba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cover Genius</t>
+          <t>Feathr</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, Git, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1ace319434b29</t>
+          <t>https://www.indeed.com/viewjob?jk=79152daad584168a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI/ML Engineer, Production AI (Contractor)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cadre5</t>
+          <t>Legend Biotech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350fed14bf8fbead</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dc6ba29ac20de2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend - Platform (Overseer)</t>
+          <t>Automations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Docker, AKS, Kafka, MongoDB, R</t>
+          <t>RAG, Prompt Engineering, S3, Athena, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7347970c571437b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c09c7f5e33db0ab</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - SDLC, GenAI</t>
+          <t>Sr. Automation Test Engineer - Playwright with Typescript</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, AKS, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb2f369f691c242</t>
+          <t>https://www.indeed.com/viewjob?jk=30d7c23c7ea6cc20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Development Eng</t>
+          <t>Accelerator Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, MLflow, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b853965575396d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4839f4dc6c0fb3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Development Eng</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Databricks, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d119a8e84a74e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analyst, Applied AI Solutions</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Bessemer Trust</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,77 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecd19983b185544</t>
+          <t>https://www.indeed.com/viewjob?jk=398baa279f08aced</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HNTB Corporation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49d8590049c7f79</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Borrow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b106e25fc9641181</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-08.xlsx
+++ b/daily_matches/job_matches_2026-04-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Palantir AI Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Glue, CI/CD, Git, Databricks</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, Glue, Athena, Redshift, Data Lake, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e23bede2bdc692</t>
+          <t>https://www.indeed.com/viewjob?jk=9f0c5b222112ed43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (AI/ML Focus)</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Pinecone, TensorFlow, PyTorch, S3, Glue, Redshift, Databricks, Redshift, Kafka</t>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8a907713e68025</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfc97622cac432</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01ec761fbfd4836</t>
+          <t>https://www.indeed.com/viewjob?jk=11c3687ade564238</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
+          <t>Copilot, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c926cca4a747050</t>
+          <t>https://www.indeed.com/viewjob?jk=e87b7bf0563dd40f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI Platform Team</t>
+          <t>Senior Software Engineer - Agentic AI - Python Expert</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, CI/CD, Git, MongoDB, SQL, R, Java</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, MLflow, FastAPI, AKS, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eebbc4bd9331ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8b93634a617e2c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Software Engineer (Hybrid Eligible)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oak Ridge National Laboratory</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, CI/CD, Python</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Docker, AKS, GitHub Actions, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c68121d4859f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=718dec0716640888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kin Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651d0a0b21d7c611</t>
+          <t>https://www.indeed.com/viewjob?jk=20cd1de8722f1e75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hunter Douglas</t>
+          <t>Simbex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Lebanon, NH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f745acfa6c4033a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa94e0905f7ecb6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer/ API Platform Engineer (AI-First)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Elsa Science</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, EC2, Kubernetes, CI/CD, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f70878f03e81d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b86f30c63e539b67</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Applied Machine Learning Engineer II - Advanced Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d608da55724e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d977c6bdae1ed8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, Video Input/Output Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Electrosoft</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
+          <t>RAG, Kubernetes, Terraform, Python, SQL, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424ec8adc24cf26f</t>
+          <t>https://www.indeed.com/viewjob?jk=229f260da23bb266</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full Stack JavaScript Engineer (Python, AWS, AI Tooling)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SWBC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25d100d0ad919c12</t>
+          <t>https://www.indeed.com/viewjob?jk=4254fd012f82d570</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Real-Time Communications (CCaaS)</t>
+          <t>Senior Full Stack JavaScript Engineer (Python, AWS, AI Tooling)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Port Richey, FL, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638e82497dbabdbe</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cfe12b50e418bc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Innovation Software Engineer L3</t>
+          <t>Software Engineer - Application Framework</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Octus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Kafka, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84788d0b728d3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=f90d5507c7396fd7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Technical Advisor, Intellectual Property</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Feathr</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, Git, MongoDB, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79152daad584168a</t>
+          <t>https://www.indeed.com/viewjob?jk=1aabaee6dd4e8d85</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer, Production AI (Contractor)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Legend Biotech</t>
+          <t>CorVel Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, RAG, AWS SageMaker, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc6ba29ac20de2</t>
+          <t>https://www.indeed.com/viewjob?jk=0882ed38fe96c668</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Automations Engineer</t>
+          <t>MRM Senior Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Athena, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, Copilot, Git, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c09c7f5e33db0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ef43e4905e01fd3a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Automation Test Engineer - Playwright with Typescript</t>
+          <t>Data Scientist Senior - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,192 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Scala</t>
+          <t>Data Scientist, AWS SageMaker, Azure ML, MongoDB, Cassandra, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d7c23c7ea6cc20</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Accelerator Architect</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CyberArk</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4839f4dc6c0fb3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5c8707df585c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bessemer Trust</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Woodbridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=398baa279f08aced</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HNTB Corporation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d49d8590049c7f79</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Borrow</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b106e25fc9641181</t>
+          <t>https://www.indeed.com/viewjob?jk=bb09201135b23379</t>
         </is>
       </c>
     </row>
